--- a/Elevator_All_Models_DB_FULLDATA_v07_ModelSheets.xlsx
+++ b/Elevator_All_Models_DB_FULLDATA_v07_ModelSheets.xlsx
@@ -444,8 +444,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1412"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:T1434"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -47056,6 +47056,732 @@
         <v>6</v>
       </c>
     </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1413" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1413" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1414" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1414" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1415" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1415" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1416" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1416" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1417" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1417" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1418" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1418" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1419" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1419" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1420" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1420" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1421" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1421" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1422" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1422" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>MELCO</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1423" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1423" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1424" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1424" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1425" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1425" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1426" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1426" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1427" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G1427" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1428" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1428" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1429" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1429" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1430" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1430" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1431" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G1431" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1432" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1432" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1433" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1433" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>NexWay-S</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>China [MESE]</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>EN81-20/50</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>Passenger elevator</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>Machine room</t>
+        </is>
+      </c>
+      <c r="F1434" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1434" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47068,7 +47794,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G95"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -50230,7 +50956,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -50356,7 +51082,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G86"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -53221,7 +53947,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G198"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -59782,7 +60508,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G69"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -62086,7 +62812,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -62278,7 +63004,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G349"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -73822,7 +74548,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -75664,7 +76390,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -76384,7 +77110,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G103"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -79810,7 +80536,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -80860,7 +81586,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G142"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -85573,7 +86299,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -86227,7 +86953,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -86683,7 +87409,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -87073,7 +87799,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -89113,7 +89839,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -89503,7 +90229,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G121"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -93523,7 +94249,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
